--- a/data/trans_dic/P1412-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1412-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,9</t>
+          <t>0,31; 2,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,04</t>
+          <t>0,36; 2,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,07</t>
+          <t>0,07; 0,84</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,22</t>
+          <t>0,39; 2,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,67</t>
+          <t>0,18; 1,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,61</t>
+          <t>0,19; 1,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,59</t>
+          <t>0,19; 1,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,11</t>
+          <t>0,11; 1,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,13</t>
+          <t>0,19; 1,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,53</t>
+          <t>0,3; 1,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,11</t>
+          <t>0,26; 1,12</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -903,17 +903,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,98</t>
+          <t>0,63; 2,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,27</t>
+          <t>0,44; 2,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,14</t>
+          <t>0,72; 2,14</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -1013,42 +1013,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,96</t>
+          <t>0,5; 3,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,96</t>
+          <t>0,89; 3,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,12</t>
+          <t>0,5; 3,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,39</t>
+          <t>0,24; 2,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,95</t>
+          <t>0,42; 2,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,91</t>
+          <t>0,51; 2,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,7</t>
+          <t>0,46; 1,95</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 7,35</t>
+          <t>0,86; 6,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,52</t>
+          <t>0,48; 3,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,54</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,26</t>
+          <t>0,8; 3,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1253,22 +1253,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,85</t>
+          <t>0,27; 1,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,51</t>
+          <t>0,18; 1,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,14</t>
+          <t>0,64; 2,03</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,81</t>
+          <t>0,3; 1,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,94</t>
+          <t>0,18; 1,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,28</t>
+          <t>0,51; 2,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,57</t>
+          <t>0,15; 1,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,37</t>
+          <t>0,5; 2,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,03</t>
+          <t>0,43; 1,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,38</t>
+          <t>0,33; 1,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,77</t>
+          <t>0,5; 1,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,27</t>
+          <t>0,58; 1,49</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,42</t>
+          <t>0,14; 1,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,51</t>
+          <t>0,26; 1,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,84</t>
+          <t>0,14; 1,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,36</t>
+          <t>0,14; 1,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,07</t>
+          <t>0,13; 1,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,16</t>
+          <t>0,23; 1,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,04</t>
+          <t>0,21; 1,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,04</t>
+          <t>0,26; 1,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,79</t>
+          <t>0,25; 0,86</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,02</t>
+          <t>0,41; 1,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,1</t>
+          <t>0,5; 1,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,23</t>
+          <t>0,68; 1,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,04</t>
+          <t>0,45; 1,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,85</t>
+          <t>0,31; 0,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,69</t>
+          <t>0,39; 0,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,93</t>
+          <t>0,52; 0,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,87</t>
+          <t>0,45; 0,86</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,85</t>
+          <t>0,59; 0,93</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>469</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2036</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>950; 8546</t>
+          <t>925; 8681</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6534</t>
+          <t>0; 7410</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5868</t>
+          <t>0; 5319</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 6574</t>
+          <t>0; 6544</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5210</t>
+          <t>0; 5820</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2506</t>
+          <t>0; 2445</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2009; 11885</t>
+          <t>2072; 12541</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 9390</t>
+          <t>0; 7606</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>408; 6421</t>
+          <t>469; 5357</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>6221</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6999</t>
+          <t>0; 6359</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1766; 11144</t>
+          <t>1959; 13105</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>925; 8609</t>
+          <t>948; 9649</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>990; 8437</t>
+          <t>994; 8812</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>996; 8335</t>
+          <t>1000; 9624</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>577; 5715</t>
+          <t>591; 6248</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2020; 11615</t>
+          <t>1994; 11501</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3306; 15669</t>
+          <t>3062; 15428</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2634; 11451</t>
+          <t>2786; 12057</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>8353</t>
         </is>
       </c>
     </row>
@@ -2192,17 +2192,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4815</t>
+          <t>0; 5421</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1989; 9418</t>
+          <t>1988; 9441</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5549</t>
+          <t>0; 6037</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2212,22 +2212,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1634; 7919</t>
+          <t>1551; 7648</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6636</t>
+          <t>0; 5514</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5307</t>
+          <t>0; 5425</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4694; 14247</t>
+          <t>4863; 14405</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>431</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6391</t>
+          <t>7275</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 7706</t>
+          <t>0; 7715</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1801; 10945</t>
+          <t>1857; 11672</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2504; 12371</t>
+          <t>3314; 14349</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2086; 12123</t>
+          <t>1956; 11849</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>937; 9237</t>
+          <t>939; 9553</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2170</t>
+          <t>0; 2373</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3214; 14878</t>
+          <t>3176; 15243</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3903; 14428</t>
+          <t>3868; 15393</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2874; 13422</t>
+          <t>3658; 15513</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>730</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>730</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2087; 15636</t>
+          <t>1823; 14546</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4113</t>
+          <t>0; 4123</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4817</t>
+          <t>0; 5384</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2538,22 +2538,22 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2203</t>
+          <t>0; 2534</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2067; 15213</t>
+          <t>2073; 16181</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4098</t>
+          <t>0; 4088</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2497</t>
+          <t>0; 2315</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6528</t>
+          <t>6434</t>
         </is>
       </c>
     </row>
@@ -2681,17 +2681,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6157</t>
+          <t>0; 6370</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2154; 8796</t>
+          <t>2159; 9001</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>973; 8245</t>
+          <t>970; 8235</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,22 +2701,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>587; 4736</t>
+          <t>715; 4499</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>977; 8362</t>
+          <t>976; 8506</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 6895</t>
+          <t>0; 6542</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3786; 11234</t>
+          <t>3429; 10848</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>6790</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>11004</t>
+          <t>14761</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2001; 12017</t>
+          <t>2018; 11404</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1184; 12716</t>
+          <t>1200; 11987</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2984; 14215</t>
+          <t>3690; 15112</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1307; 10876</t>
+          <t>1054; 10569</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3516; 16377</t>
+          <t>3482; 16642</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1428; 8706</t>
+          <t>3314; 12058</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4475; 18756</t>
+          <t>4420; 18093</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6790; 23899</t>
+          <t>6780; 22869</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5613; 18712</t>
+          <t>8589; 22131</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>6946</t>
+          <t>7833</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1137; 11042</t>
+          <t>1128; 10910</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2091; 11766</t>
+          <t>1997; 12640</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>634; 7771</t>
+          <t>1131; 8507</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1077; 11185</t>
+          <t>1157; 10581</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1066; 8844</t>
+          <t>1070; 9411</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1770; 8326</t>
+          <t>1876; 8778</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4282; 16665</t>
+          <t>3420; 16048</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4606; 16732</t>
+          <t>4116; 16783</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2986; 12997</t>
+          <t>4032; 13960</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>30153</t>
+          <t>32671</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17930</t>
+          <t>20972</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>48083</t>
+          <t>53643</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>14015; 34907</t>
+          <t>14192; 34240</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>16843; 37325</t>
+          <t>16958; 38075</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21197; 42526</t>
+          <t>23976; 45421</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16104; 37053</t>
+          <t>16087; 36747</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>10542; 30233</t>
+          <t>11125; 30679</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12410; 25356</t>
+          <t>14728; 28149</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34978; 64582</t>
+          <t>35976; 65540</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>33386; 60484</t>
+          <t>31245; 59836</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>36207; 60708</t>
+          <t>42561; 67365</t>
         </is>
       </c>
     </row>
